--- a/research/JBK_Consumer_Probiotic_Prospects_2026-10-05.xlsx
+++ b/research/JBK_Consumer_Probiotic_Prospects_2026-10-05.xlsx
@@ -21,17 +21,17 @@
     <sheet name="Already_Enriched" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shortlist'!$A$1:$T$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product_Evidence'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Manufacturer_Map'!$A$1:$K$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CMO_Prospects'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Contacts'!$A$1:$N$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Competitor_Strains'!$A$1:$J$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Facts_Inferences_Unknowns'!$A$1:$E$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Low_Fit_Excluded'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Sources'!$A$1:$D$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Method_Notes'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Apollo_Lookup_Queue'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Shortlist'!$A$1:$T$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product_Evidence'!$A$1:$O$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Manufacturer_Map'!$A$1:$K$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CMO_Prospects'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Contacts'!$A$1:$N$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Competitor_Strains'!$A$1:$J$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Facts_Inferences_Unknowns'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Low_Fit_Excluded'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Sources'!$A$1:$D$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Method_Notes'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Apollo_Lookup_Queue'!$A$1:$G$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Already_Enriched'!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Fast&amp;Up</t>
+          <t>Fast&amp;Up; Chicnutrix</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Plant Protein (6 flavours, 500 g/1 kg/sachets); Yeast Protein (4 variants); Multivitamin Men/Women with Probiotics</t>
+          <t>Plant Protein (6 flavours, 500 g/1 kg/sachets); Yeast Protein (4 variants); Multivitamin Men/Women with Probiotics; Chicnutrix Plant Protein (Rich Chocolate 500 g/1 kg/sachet)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -711,7 +711,10 @@
           <t>https://www.fastandup.in/products/plant-protein-rich-chocolate-1kg
 https://cdn.shopify.com/s/files/1/0574/6035/9243/files/2_0fb2ebd3-8471-475d-86f7-ad5dd911696a.jpg
 https://cdn.shopify.com/s/files/1/0574/6035/9243/files/slide8_1.jpg
-https://cdn.shopify.com/s/files/1/0574/6035/9243/files/6_d81fc36c-9001-4828-9e3d-4d88f416fdc6.png</t>
+https://cdn.shopify.com/s/files/1/0574/6035/9243/files/6_d81fc36c-9001-4828-9e3d-4d88f416fdc6.png
+https://chicnutrix.com/products/plant-protein-rich-chocolate-1kg
+https://cdn.shopify.com/s/files/1/0876/3490/3327/files/6_b9e239c5-819b-4be6-970e-e27a1c2e2a2f.png
+https://cdn.shopify.com/s/files/1/0876/3490/3327/files/J.jpg</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -939,67 +942,67 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Dead Honest</t>
+          <t>AS-IT-IS (ATOM)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Company owning GSTIN 08AALCD6762C1ZJ (legal name not confirmed), Alwar, Rajasthan</t>
+          <t>Medizen Labs Pvt Ltd, Bengaluru (owner per site terms; also the manufacturer on labels)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Fermented Probiotic Beverage 250 ml can; Fermented Probiotic Shots 60 ml</t>
+          <t>ATOM NXT Yeast Protein (several flavours, 500 g / 1 kg)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>B. coagulans (strain ID said to be on the can; not published online) + LAB from water-kefir fermentation</t>
+          <t>B. coagulans (strain not declared), with DigeZyme®</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2 bn CFU per can (website)</t>
+          <t>1 bn CFU per serve</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>In-house: H1-336(A) RIICO Industrial, Khushkhera, Alwar (Bhiwadi), Rajasthan 301707</t>
+          <t>Medizen Labs Pvt Ltd, No. 104/4, 1st Cross, NTY Layout, Avalahalli, Mysore Road, Bengaluru 560026</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Verified (official website)</t>
+          <t>Verified (pack labels + site terms)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Own fermentation plant: buys the probiotic directly (website says ingredients come from 'verified and certified suppliers')</t>
+          <t>Own manufacturing: Medizen Labs buys directly (inferred from owner = manufacturer)</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Co-founders (Jasleen, Kisslay, Amrit)</t>
+          <t>Medizen Labs R&amp;D (unknown names)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Co-founders/production (inferred, small team)</t>
+          <t>Medizen Labs purchasing (inferred)</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Jasleen, Kisslay, Amrit (co-founders; first names only)</t>
+          <t>None found</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>B (official site text); strain not seen</t>
+          <t>A (labels)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Unknown: strain not public</t>
+          <t>None declared (ATOM whey uses LAB 1 bn CFU)</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1009,18 +1012,20 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Which B. coagulans strain/supplier is on the can, and is it locked by a clinical claim?</t>
+          <t>Who supplies the B. coagulans now? Would they move ATOM whey from LAB to Bacillus?</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Get a current can image (ChatGPT workbook or retail) to read the strain ID. Run an Apollo lookup to resolve co-founder surnames. Position PRODURA B. coagulans for heat and shelf stability in a canned RTD</t>
+          <t>Apollo lookup on Medizen Labs R&amp;D/purchase. Pitch PRODURA B. coagulans for NXT and a Bacillus switch for ATOM whey</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>https://www.deadhonest.in/about
-https://www.deadhonest.in/faqSection</t>
+          <t>https://asitisnutrition.com/products/as-it-is-atom-nxt-protein
+https://cdn.shopify.com/s/files/1/0005/5335/3267/files/ATOM_NXT_Protein_500g_Kesar_Kulfi_Product_Side_Gusset_Image_3bcb4e83-542d-4910-996b-e49d66e27533.jpg
+https://cdn.shopify.com/s/files/1/0005/5335/3267/files/ATOM_Whey_Protein_With_Yeast_1kg_Double_Rich_Chocolate_Side_Gusset_1.jpg
+https://asitisnutrition.com/policies/terms-of-service</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1040,85 +1045,186 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>Dead Honest</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Company owning GSTIN 08AALCD6762C1ZJ (legal name not confirmed), Alwar, Rajasthan</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Fermented Probiotic Beverage 250 ml can; Fermented Probiotic Shots 60 ml</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>B. coagulans (strain ID said to be on the can; not published online) + LAB from water-kefir fermentation</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2 bn CFU per can (website)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>In-house: H1-336(A) RIICO Industrial, Khushkhera, Alwar (Bhiwadi), Rajasthan 301707</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Verified (official website)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Own fermentation plant: buys the probiotic directly (website says ingredients come from 'verified and certified suppliers')</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Co-founders (Jasleen, Kisslay, Amrit)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Co-founders/production (inferred, small team)</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Jasleen, Kisslay, Amrit (co-founders; first names only)</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>B (official site text); strain not seen</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Unknown: strain not public</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Which B. coagulans strain/supplier is on the can, and is it locked by a clinical claim?</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Get a current can image (ChatGPT workbook or retail) to read the strain ID. Run an Apollo lookup to resolve co-founder surnames. Position PRODURA B. coagulans for heat and shelf stability in a canned RTD</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.deadhonest.in/about
+https://www.deadhonest.in/faqSection</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>Organic India</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Organic India Pvt Ltd (Tata Consumer Products since 2024)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Revitalise Gut herbal tea; Sat Isabgol Capsules; (Sat Isabgol Pre &amp; Probiotic Fibre Powder: organism not verified)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>B. coagulans (strain not declared)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Revitalise Gut: 1 bn CFU per 3 serves (label ingredient 0.036 g B. coagulans); Sat Isabgol Capsules: 1 bn CFU</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Organic India Pvt Ltd, C-5/10 Agro Park Ph-II, UPSIDC, Kursi Road, Barabanki, UP 225302 (capsules: label). Tea: manufacturing unit given by QR/batch code</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Verified for capsules; tea unit unresolved</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>In-house plant (Barabanki) for capsules. Purchasing likely through Organic India or Tata Consumer procurement (inferred)</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Organic India / TCPL R&amp;D (inferred)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Organic India or TCPL procurement (unknown which)</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>No named contact found; generic care@tataconsumer.com (label)</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>A (labels)</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>Who owns probiotic vendor approval after the TCPL integration?</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>Run an Apollo lookup on Organic India and Tata Consumer R&amp;D, sourcing and nutraceutical roles. Propose PRODURA B. coagulans for the isabgol and tea range, and B. subtilis for new fibre SKUs</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>https://organicindia.com/products/revitalise-gut
 https://cdn.shopify.com/s/files/1/0663/6286/8029/files/Revitalisegut_side2.png
@@ -1127,102 +1233,102 @@
 https://www.tataconsumer.com/news/tata-consumer-products-acquire-organic-india-better-you-organic-brand-spanning-food-beverages</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Protyze</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Alphacentric Healthcare Pvt Ltd, Bengaluru</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Diet Clear Whey Protein Isolate with Probiotics (Mango, Lychee, Blueberry; 15/30 servings; assorted)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>6-strain blend: L. acidophilus, L. rhamnosus, B. longum, B. bifidum, S. thermophilus, 'Lactic acid bacillus' (Indian label name usually used for B. coagulans; inference)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Each &gt;0.75 bn CFU; 4.5 bn CFU per serve (500 mg probiotic mixture)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Own manufacturing unit set up Nov 2023 (press); plant address not seen on pack images</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Secondary (press), not on label</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Alphacentric buys directly if the unit is its own (inferred)</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Founder Vinit Kumar / R&amp;D team</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Procurement (IndiaMART lists a Procurement cum Admin Executive)</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Nayana (Procurement cum Admin Executive), Vinit Kumar (Founder)</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>A (label) for organisms; B/C for manufacturing</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>No named competitor strain</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>Is 'Lactic acid bacillus' a B. coagulans single-strain bought separately or a pre-blended LAB mix? Who supplies it?</t>
         </is>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>Run an Apollo lookup on Alphacentric Healthcare. Propose a Bacillus-only clear-whey version (spore stability in acidic clear whey) or swapping the 'Lactic acid bacillus' component to PRODURA</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>https://www.protyze.com/products/diet-clear-protein-juicy-mango-30-serving
 https://cdn.shopify.com/s/files/1/0293/5291/9093/files/Artboard_1_16_ea9c4ef4-3467-44e2-ad9c-de006a3b5b81.avif
@@ -1230,102 +1336,204 @@
 https://www.indiamart.com/alphacentric-healthcare-private-limited/whey-protein.html</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>MuscleBlaze; Gritzo (HealthKart)</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Bright Lifecare Pvt Ltd (HealthKart)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Biozyme Gold 100% Whey; Gritzo SuperMilk kids' nutrition drinks (e.g. Weight+ 13+)</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Biozyme Gold BiomePro™: S. boulardii, L. rhamnosus, B. coagulans, B. clausii, B. subtilis. Gritzo SuperMilk: B. coagulans (strains not declared)</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Biozyme Gold: 1 bn CFU/serve (total). Gritzo SuperMilk: 1 bn CFU B. coagulans (search snippet; official page lists the organism)</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Gritzo: Sapiens Labs, Village Dhana Bagbania, PO Manpura, Tehsil Nalagarh, Solan, HP 174101 (official page). Biozyme: unverified (snippets name Twilight Litika Pharma at the same village, or Zeon Lifesciences, Paonta Sahib)</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Gritzo verified (official page); Biozyme unverified</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Contract manufactured (Sapiens Labs for Gritzo). Brand-owned blends, so Bright Lifecare likely nominates strains (inference)</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Bright Lifecare R&amp;D (30-member team reported)</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Maheshwari (CEO; not a formulation contact)</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>A/B (Gritzo official page); B- (Biozyme reseller page)</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>Does Bright Lifecare nominate probiotic suppliers to Sapiens Labs and other CMOs, and who in its R&amp;D team owns this?</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>Apollo lookup on Bright Lifecare R&amp;D/sourcing. Approach Sapiens Labs as a CMO (also makes Little Joys). Offer a three-organism supply for BiomePro and B. coagulans for Gritzo</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gritzo.com/products/supermilk-weight-plus
+https://prostarnutrition.in/product/muscleblaze-mb-biozyme-gold-100-whey-protein-isolate/
+https://www.nutraingredients.com/Article/2025/03/04/muscleblaze-to-ramp-up-whey-protein-sports-nutrition-business-with-us-patent/</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>The Good Bug</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Seven Turns Pvt Ltd, Mumbai</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Multivitamin + Probiotics (Men/Women/Men&amp;Women); Berberine + Probiotics; Magnesium + Probiotics (tablets)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>B. coagulans (strain not declared)</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1 bn CFU per serve (multivitamin, berberine); magnesium qty illegible</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Nutricore Biosciences Pvt Ltd, Plot 10-26 Sky Industries, Lindiad, Surat, Gujarat 394530 (multivitamin, magnesium labels)</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Verified for multivitamin &amp; magnesium; berberine inferred</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Brand-specified, CMO-made: Nutricore may buy on Seven Turns' spec (turnkey) or Seven Turns may nominate the supplier (unknown)</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>Seven Turns R&amp;D/NPD (named team)</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>Unknown: Seven Turns vs Nutricore</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Dr Abhishek Kanade, Shruti Sankpal, Sanjana Sawant, Ricky Marfatia, Arpita Pandirkar</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>A (labels + official team page)</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>No (sachet range uses LGG/Microbac from Sundyota Numandis: not Bacillus)</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>Does Seven Turns nominate the probiotic vendor to Nutricore, or does Nutricore source it?</t>
         </is>
       </c>
-      <c r="R8" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>Approach on two tracks: (1) Seven Turns NPD (Kanade/Sankpal/Sawant) for strain nomination; (2) Nutricore purchasing for tablet supply. Apollo lookup on named NPD leads</t>
         </is>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>https://thegoodbug.com/products/multivitamin-probiotics
 https://cdn.shopify.com/s/files/1/0657/8225/1745/files/Multivitamin__Women_BOP-Amazon.png
@@ -1336,204 +1544,513 @@
 https://thegoodbug.com/pages/our-experts</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness Company, Makali, Bengaluru</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Healthy Gut Probiotic Gummies (30s/60s); Florasante capsules</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Gummies: B. subtilis HS43. Florasante: B. coagulans (strain not declared) + B. subtilis TO-A + S. thermophilus St-21</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Gummies: 1.5 bn CFU/gummy (3 bn/serve). Florasante: B. coagulans 100 million, B. subtilis TO-A 10 million, St-21 1 bn CFU</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Gummies: Sarvotham Care Ltd, Jeedipally Village, Medak, Telangana 502334. Florasante: Allianz Biosciences Pvt Ltd, Thiruvandar Koil, Puducherry 605102</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Verified (pack labels + official page)</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Contract manufactured. Named strains suggest Himalaya specifies the strains; who buys them is unknown</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Himalaya R&amp;D (Bengaluru)</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Unknown: Himalaya vs CMOs</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>No named contact; label route 'Manager - Customer Care'</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>A (labels)</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>Named strains HS43 and TO-A (suppliers not verified)</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>Is Himalaya open to a second Bacillus source for new SKUs? Who owns probiotic vendor approval?</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>Apollo lookup on Himalaya Wellness R&amp;D/sourcing (probiotics). Approach Sarvotham Care and Allianz Biosciences as CMOs</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>https://himalayawellness.in/products/healthy-gut-probiotic-gummies
+https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-30s-SIDE1-INDIA-13750-F39-FV.jpg
+https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-60s-SIDE3-INDIA-13750-F39-FV.jpg
+https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-30s-SIDE2-INDIA-13750-F39-FV.jpg
+https://himalayawellness.in/products/florasante
+https://cdn.shopify.com/s/files/1/0272/4714/9155/files/FLORASANTECAPSULES10sBOTTLESIDE1INDIA15027RGBIMSJHI2600217.jpg
+https://cdn.shopify.com/s/files/1/0272/4714/9155/files/FLORASANTECAPSULES10sCARTONSIDE1INDIA15027RGBIMSJHI2600217.jpg</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Max Protein; Complan (Zydus Wellness)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Zydus Wellness Ltd, Ahmedabad</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Max Protein Plant Protein (Swiss Chocolate, Creamy Vanilla, Alphonso Mango); Complan VieMax</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Max Protein: Pepzyme Pro (protease + B. coagulans, B. subtilis, B. clausii). Complan VieMax: B. coagulans Unique IS-2</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Not declared in captured text</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Max Protein: Yummy Food Specialities Pvt (FSSAI 10018047001013) per official page. Complan VieMax: not seen</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Verified for Max Protein (official page)</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Max Protein: CMO-made with a supplier premix. Complan: competitor strain</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Zydus Wellness R&amp;D</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>A (labels) / B (pharmacy listing for Complan)</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>YES: Unique IS-2 (Complan); Pepzyme Pro (Max Protein)</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>Who in Zydus Wellness owns probiotic sourcing across brands?</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>Apollo lookup on Zydus Wellness R&amp;D/procurement. Pitch a three-organism alternative to the premix, and alternate-strain work on Complan</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.maxprotein.in/products/max-protein-plant-protein-swiss-chocolate
+https://cdn.shopify.com/s/files/1/0512/8827/7146/files/ingradients_8199a49a-8c11-47db-bf73-855260d96aa5.jpg
+https://www.apollopharmacy.in/otc/complan-viemax-vanilla-flavour-400g-jar</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>SuperYou</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>SuperYou brand (Ranveer Singh &amp; Nikunj Biyani; legal entity not confirmed)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Fermented Yeast Protein (Chocolate, Cold Coffee, Unflavoured, Vanilla, Kesar Badam, Strawberry; jars &amp; sachets)</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>B. coagulans (strain not declared)</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>1 bn CFU per serve</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Saipro Industries Pvt Ltd, Kasaramboli, Mulshi, Pune (Choc, Cold Coffee, Unflav, Vanilla); H&amp;H Healthcare &amp; Cosmetics Pvt Ltd, Smart Industrial Park, Dhar, MP (Kesar Badam, Strawberry)</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Verified (official manufacturer page)</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Two CMOs; buyer of probiotic unknown (brand-nominated vs CMO-sourced)</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>SuperYou product team (unknown)</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Unknown: SuperYou vs Saipro / H&amp;H</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>Nikunj Biyani (co-founder)</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N13" s="3" t="inlineStr">
         <is>
           <t>A (label + official manufacturer page)</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>Does SuperYou specify the B. coagulans supplier to both CMOs?</t>
         </is>
       </c>
-      <c r="R9" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>Run an Apollo lookup on the SuperYou NPD/sourcing lead. Approach Saipro, which also makes Plix and Naturaltein products, as a hub CMO</t>
         </is>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t>https://superyou.in/products/chocolate-protein-powder
 https://cdn.shopify.com/s/files/1/0902/2590/1858/files/1kg_Chocolate_Ingredients_1.jpg
 https://superyou.in/pages/manufacturer-details</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Little Joys</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Mosaic Wellness Pvt Ltd, Thane</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Nutrimix 7+ &amp; MamaMix nutrition powders; Nutrimix Lite (5 bn CFU, organism not verified)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Digestion blend: L. acidophilus, B. infantis, B. bifidum, B. coagulans, L. rhamnosus (strains not declared)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Not declared per organism</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Sapiens Labs, Bagbania, Village Dhana, PO Manpura, Tehsil Baddi, Solan, HP 174101 (official page)</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Verified (official page)</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Contract manufactured (Sapiens Labs); buyer unknown</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Mosaic Wellness R&amp;D</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>B (official page text)</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>None declared</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>Who specifies the probiotic blend: Mosaic Wellness or Sapiens Labs?</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>Apollo lookup on Mosaic Wellness R&amp;D (kids nutrition). Approach Sapiens Labs as a hub CMO</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>https://ourlittlejoys.com/product/mamamix-nutrimix-7
+https://ourlittlejoys.com/product/nutrimix-lite-1kg</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Hack Daily</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>SnappySoul Pvt Ltd, New Delhi</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>HACK GUT daily gut-care drink sachet</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>B. coagulans + B. subtilis (strains not declared)</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>B. coagulans 2 bn CFU + B. subtilis 1 bn CFU per serve</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Hack Gut: not seen. Sister product Hack Lean: Gangwal Healthcare Pvt Ltd, MIDC Tarapur, Boisar, Palghar</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Inferred for Hack Gut (same brand CMO)</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Contract manufactured (inferred Gangwal); buyer unknown</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>SnappySoul founders/product team</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Unknown: SnappySoul vs Gangwal</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>Tanmay Taneja, Rajat Sachdeva (co-founders; unverified)</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>B (official page text) for organisms; A for Hack Lean CMO</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>Confirm Hack Gut manufacturer and who buys the two Bacillus strains</t>
         </is>
       </c>
-      <c r="R10" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>Get the Hack Gut back-of-pack (ChatGPT workbook / retail) for strain and manufacturer. Approach Gangwal Healthcare as CMO prospect</t>
         </is>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>https://hackdailylife.com/products/hack-gut
 https://hackdailylife.com/products/hack-lean
@@ -1541,406 +2058,305 @@
 https://hackdailylife.com/pages/contact</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>MuscleBlaze (Biozyme Gold)</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Bright Lifecare Pvt Ltd (HealthKart)</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Biozyme Gold 100% Whey</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>BiomePro™: S. boulardii, L. rhamnosus, B. coagulans, B. clausii, B. subtilis (strains not declared)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>1 bn CFU per serve (total)</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Unverified: search snippets name Twilight Litika Pharma (Baddi, HP) / Zeon Lifesciences (Paonta Sahib, HP)</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Unverified (secondary)</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Contract manufactured (inferred); BiomePro is a brand-owned blend, so the brand likely nominates strains (inference)</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>Bright Lifecare R&amp;D (30-member team reported)</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>Sameer Maheshwari (CEO; not a formulation contact)</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>B- (authorised reseller page)</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Origin Nutrition</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Origin Nutrition Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Kids Nutrition Mix (Chocolate Fudge, Creamy Vanilla, Cotton Candy Swirl; ages 3-6, 7-12, 13+)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>B. coagulans (strain not declared)</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Quantity on label not legible in image</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Website: 'Manufactured by Origin Nutrition Private Limited' (plant location not stated)</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Verified (site), location unknown</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Probably own or toll manufacturing; buyer unknown</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Aditi Mammen Gupta (Founder, food formulator)</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Chirag Gupta (Co-founder; 'from sourcing to delivery')</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Aditi Mammen Gupta, Chirag Gupta</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>A (labels + official about page)</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>Confirm the current pack label, manufacturer and BiomePro supplier</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>Verify from a current pack image. Run an Apollo lookup on Bright Lifecare R&amp;D/sourcing. High-volume target for tri-organism supply</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>https://prostarnutrition.in/product/muscleblaze-mb-biozyme-gold-100-whey-protein-isolate/
-https://www.nutraingredients.com/Article/2025/03/04/muscleblaze-to-ramp-up-whey-protein-sports-nutrition-business-with-us-patent/</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Origin Nutrition</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Origin Nutrition Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Kids Nutrition Mix (Chocolate Fudge, Creamy Vanilla, Cotton Candy Swirl; ages 3-6, 7-12, 13+)</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>B. coagulans (strain not declared)</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Quantity on label not legible in image</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Website: 'Manufactured by Origin Nutrition Private Limited' (plant location not stated)</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Verified (site), location unknown</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Probably own or toll manufacturing; buyer unknown</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>Aditi Mammen Gupta (Founder, food formulator)</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Chirag Gupta (Co-founder; 'from sourcing to delivery')</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>Aditi Mammen Gupta, Chirag Gupta</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>A (labels + official about page)</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>None declared</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>Where is it made, and what CFU and strain are used?</t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>Approach founders (formulator + sourcing are both named). Offer PRODURA B. coagulans for kids powders</t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="S16" s="3" t="inlineStr">
         <is>
           <t>https://originnutrition.in/products/kids-nutrition-mix-chocolate-fudge-ages-7-12
 https://cdn.shopify.com/s/files/1/0869/4051/6536/files/Infographic_cotton_candy_3-6_iv.webp
 https://originnutrition.in/pages/about-us</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Big Muscles Nutrition</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Bigmuscles Nutrition Pvt Ltd</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Whey Protein + Fiber</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>B. coagulans (in blend with fermented yeast protein isolate, FOS, bromelain)</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Not legible</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Label: 'Manufactured &amp; Marketed by Bigmuscles Nutrition Pvt Ltd'; manufacturer address via QR</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>Partly verified</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Unknown (own vs contract facility)</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>Generic: support@bigmusclesnutrition.com, +91-8882200500 (label)</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>A (label) for organism</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>Real manufacturing site and probiotic supplier</t>
         </is>
       </c>
-      <c r="R13" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>Run an Apollo lookup on Bigmuscles R&amp;D/purchase. Request the manufacturer detail behind the QR code</t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>https://bigmusclesnutrition.com/products/whey-protein
 https://cdn.shopify.com/s/files/1/0291/3743/6771/files/back-2kg.jpg</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Wellbeing Nutrition</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Nutritionalab Pvt Ltd, Mumbai</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Melts Healthy Gut (probiotic + ACV oral strips); Melts Marvel / Disney Frozen Active Probiotic kids strips</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>B. coagulans (strain not declared); kids strips also L. acidophilus</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Healthy Gut: 10 bn CFU; kids strips: 5 bn CFU B. coagulans + 2 bn L. acidophilus</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>Not found for Melts</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Unknown (Melts likely contract-made)</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>Nutritionalab NPD (NPD Specialist role advertised)</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M18" s="3" t="inlineStr">
         <is>
           <t>Avnish Chhabria (Founder), Saurabh Kapoor (Co-founder &amp; CBO)</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N18" s="3" t="inlineStr">
         <is>
           <t>A (labels)</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>Who makes Melts and supplies the B. coagulans? Would Wellbeing switch its LAB-based protein probiotics to Bacillus?</t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>Run an Apollo lookup on Nutritionalab NPD/R&amp;D. New-product angle: Bacillus in whey/plant protein (currently L. acidophilus + B. longum 4 bn)</t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t>https://wellbeingnutrition.com/products/melts-healthy-gut-probiotic-acv-oral-strips
 https://cdn.shopify.com/s/files/1/0240/2942/9840/files/IMG9_b1bad537-2ed2-4df8-887c-85ba570127c0.jpg
@@ -1950,618 +2366,720 @@
 https://cdn.shopify.com/s/files/1/0240/2942/9840/files/BOP_2kg.jpg</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>OZiva</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>OZiva (brand owner entity not confirmed in this pass)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Daily Protein Activ for Women</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>B. coagulans (strain not declared)</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>1 bn CFU per 100 g product</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>None found</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
         <is>
           <t>B (official page text)</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>None declared</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>Manufacturer and current listing status</t>
         </is>
       </c>
-      <c r="R15" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>Verify pack label and manufacturer; Apollo lookup on OZiva R&amp;D</t>
         </is>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t>https://www.oziva.in/products/daily-protein-activ-for-women-with-clean-whey-protein-multivitamins-tulsi-probiotics-for-improved-everyday-energy-stamina-bone-health-immune-health</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Plix</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Satiya Nutraceuticals Pvt Ltd, Bhiwandi (Thane)</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Happy Tummy Effervescent (pre + probiotic)</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>BC30® (B. coagulans GBI-30, 6086)</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Not shown in captured page text</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Nutralike Healthcare / Nutralike Formulation Pvt Ltd, Swagat-3 Industrial Park, Kuha, Ahmedabad, Gujarat 382433</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Verified (official page)</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>CMO-made; BC30 is a branded strain (brand-specified, inferred)</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Plix R&amp;D (not named)</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Rishubh Satiya (CEO/co-founder), Akash Zaveri (co-founder)</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>B (official page)</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>YES: BC30 (Kerry)</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Is BC30 tied to marketing claims, or would Plix approve an alternate strain for a new SKU?</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>Treat as alternate-strain or new-product opportunity only. Approach Nutralike as CMO prospect</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr">
+      <c r="S20" s="4" t="inlineStr">
         <is>
           <t>https://www.plixlife.com/product/good-gut-preprobiotics/90
 https://www.plixlife.com/product/probiotic-apple-cider-vinegar/91</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Herbalife India</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Herbalife Nutrition (India operations)</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Simply Probiotic</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>B. coagulans Unique IS-2®</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Not shown on distributor page</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Geltec (Attibele, Bangalore) and Tirupati Lifescience (Paonta Sahib, HP)</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Secondary (independent distributor page)</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Global brand spec; CMO-made</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Herbalife global R&amp;D (inferred)</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>YES: Unique IS-2</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Is India sourcing decided locally?</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>Low priority: alternate-strain discussion only via CMOs (Geltec, Tirupati)</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>https://healthforindia.goherbalife.com/Catalog/Product/Details/en-IN/025K</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>What's Up Wellness</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Wellness Ville Pvt Ltd, Kolkata</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Gut Health Gummies</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>B. coagulans Unique IS-2®</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>~0.5 bn per gummy (marketplace text; label OCR partial)</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Unique Biotech Ltd, MN Park, Kolthur, Shameerpet, Hyderabad (label)</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Verified (label)</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Strain owner is also the manufacturer: competitor-locked</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Unique Biotech (turnkey, inferred)</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Vaibhav Makhija, Sayantani Mandal (founders; unverified)</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>A (label)</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>YES: Unique IS-2 (strain owner = CMO)</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Would the brand dual-source a new SKU outside Unique Biotech?</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>Low priority: new SKU only</t>
         </is>
       </c>
-      <c r="S18" s="4" t="inlineStr">
+      <c r="S22" s="4" t="inlineStr">
         <is>
           <t>https://www.whatsupwellness.in/products/whats-up-gut-health-gummies
 https://cdn.shopify.com/s/files/1/0516/5229/6855/files/GutBack.png</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Nutrazee</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Nutrazee (brand; legal entity not confirmed)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Pre Probiotic Gummies (kids &amp; adults)</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>B. coagulans Unique IS-2®</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2 bn CFU per gummy</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Unique Biotech Ltd, MN Park, Kolthur, Shameerpet, Telangana (label)</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Verified (label)</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Strain owner is also the manufacturer: competitor-locked</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Unique Biotech (turnkey, inferred)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>A (labels)</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>YES: Unique IS-2 (strain owner = CMO)</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>Would the brand dual-source a new SKU?</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>Low priority: new SKU only</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>https://nutrazee.com/products/probiotic-prebiotic-gummies-supplement
+https://cdn.shopify.com/s/files/1/0072/8796/3757/files/8_a24f680a-a143-4974-b602-f93834a46894.jpg
+https://cdn.shopify.com/s/files/1/0072/8796/3757/files/7_58a6f5ac-c333-43c8-947e-b877cafccfcb.jpg</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Swisse India</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Health and Happiness (H&amp;H) Trading India Pvt Ltd, Bangalore (importer)</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>SwisseMe Probiotics + Prebiotic Gummies</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>B. coagulans spores (strain not declared)</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>1.5 bn CFU per gummy</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Imported; label lists Keilor Park, VIC, Australia</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Verified (label)</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Imported finished goods: no Indian ingredient purchase</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>H&amp;H global</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>H&amp;H global</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Generic: customercarein@hh.global (label)</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>A (label)</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>Any plan to make locally?</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t>Exclude unless H&amp;H localises manufacturing</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr">
+      <c r="S24" s="4" t="inlineStr">
         <is>
           <t>https://swisse.co.in/products/swisseme-probiotics-prebiotic-gummies-probiotic-supplement-with-1-5-billion-cfu-per-serving-zero-added-sugar-fridge-free-probiotic-30-gummies-one-gummy-per-serving-orange-flavour
 https://cdn.shopify.com/s/files/1/0556/6264/1337/products/Probioticgummies_amazonA_TILE5.png
 https://cdn.shopify.com/s/files/1/0556/6264/1337/products/Probioticgummies_amazonA_TILE6.png</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Naturaltein</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Naturaltein LNG Pvt Ltd, Pune</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Probiotics &amp; Prebiotics capsules (50 bn CFU)</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Strains not publicly disclosed</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>50 bn CFU</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Saipro Industries Pvt Ltd, Pune (official page)</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Verified (official page)</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>CMO-made (Saipro)</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Kawaljeet Singh (Director, grievance officer)</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>Not qualified: Bacillus use evidenced; external purchasing, acceptance of JBK ingredient and responsible buyer NOT confirmed</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>Is any Bacillus organism in the blend?</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr">
+      <c r="R25" s="4" t="inlineStr">
         <is>
           <t>Low priority: confirm strain list; reach via Saipro hub</t>
         </is>
       </c>
-      <c r="S20" s="4" t="inlineStr">
+      <c r="S25" s="4" t="inlineStr">
         <is>
           <t>https://naturaltein.in/products/probiotics-prebiotics</t>
         </is>
       </c>
-      <c r="T20" s="4" t="inlineStr">
+      <c r="T25" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T20"/>
+  <autoFilter ref="A1:T25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2572,7 +3090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2623,7 +3141,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>1) Pulled official product catalogues (Shopify product feeds) for 12 named brands plus ~70 other Indian brand sites; 2) OCR'd ~1,750 official pack/label images from brand CDNs (Tesseract), with visual checks of key labels; 3) read official pages for 'Manufactured by'/'Marketed by'; 4) used web search for company, CMO and people evidence; 5) separated label facts from press, directory and search-snippet claims.</t>
+          <t>1) Pulled official product catalogues (Shopify product feeds) for 12 named brands plus ~70 other Indian brand sites; 2) OCR'd ~1,750 official pack/label images from brand CDNs (Tesseract), with visual checks of key labels; 3) read official pages for 'Manufactured by'/'Marketed by'; 4) used web search for company, CMO and people evidence; 5) separated label facts from press, directory and search-snippet claims. Round 2 (same day): scanned ~230 more brand domains, OCR'd ~530 more label images and searched large FMCG/pharma consumer brands.</t>
         </is>
       </c>
     </row>
@@ -2642,89 +3160,101 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Qualification rule</t>
+          <t>Tiers</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>No company is marked a qualified buyer. Every prospect is 'Not qualified' until there is evidence of (a) external purchase of the probiotic, (b) acceptance of JBK's ingredient and (c) a confirmed responsible buyer.</t>
+          <t>Tier 1 = Bacillus use verified on the label AND the brand owner manufactures in-house (direct purchase likely). Tier 2 = Bacillus use verified but made by a contract manufacturer, or the buyer is unclear. Tier 3 = competitor strain locked in, imported, or strains undisclosed.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>'Lactic acid bacillus'</t>
+          <t>Qualification rule</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Indian labels often use this for B. coagulans (formerly 'Lactobacillus sporogenes'). Treated as an inference, not proof.</t>
+          <t>No company is marked a qualified buyer. Every prospect is 'Not qualified' until there is evidence of (a) external purchase of the probiotic, (b) acceptance of JBK's ingredient and (c) a confirmed responsible buyer.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Contacts</t>
+          <t>'Lactic acid bacillus'</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Names and roles are recorded only where a source supports them; the evidence strength is shown for each. No emails or phone numbers were guessed. Only routes published on official sites or labels are listed (many are consumer-care routes, marked as such).</t>
+          <t>Indian labels often use this for B. coagulans (formerly 'Lactobacillus sporogenes'). Treated as an inference, not proof.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Contacts</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>No Apollo searches or enrichment were run and no credits were spent. Contacts marked 'Suitable for Apollo lookup' are candidates for the user's own lookup. 'Enrichment completed?' = No for all.</t>
+          <t>Names and roles are recorded only where a source supports them; the evidence strength is shown for each. No emails or phone numbers were guessed. Only routes published on official sites or labels are listed (many are consumer-care routes, marked as such).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>No outreach</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>No company was contacted and no messages were sent.</t>
+          <t>No Apollo searches or enrichment were run and no credits were spent. Contacts marked 'Suitable for Apollo lookup' are candidates for the user's own lookup. 'Enrichment completed?' = No for all.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>OCR caveat</t>
+          <t>No outreach</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>OCR can misread small text. Quantities marked 'illegible' were not guessed. Key competitor-strain and CFU claims (Yogabar SNZ 1969; Yogabar whey CFU; Protyze blend) were visually confirmed.</t>
+          <t>No company was contacted and no messages were sent.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>OCR caveat</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>OCR can misread small text. Quantities marked 'illegible' were not guessed. Key competitor-strain and CFU claims (Yogabar SNZ 1969; Yogabar whey CFU; Protyze blend) were visually confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>Not covered</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Amazon/Flipkart/1mg pages were mostly bot-blocked; offline-only brands and private-label B2B were not mapped. Pepzyme Pro supplier's group link to Advanced Enzyme Technologies is an inference to verify.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2735,7 +3265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3931,8 +4461,45 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>C35</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Sapiens Labs</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>D.K. Malhotra</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Founder (per directory listing)</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>C (unverified)</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Suitable for Apollo lookup</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G32"/>
+  <autoFilter ref="A1:G33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4019,7 +4586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7051,8 +7618,766 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>P40</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Chicnutrix (Fullife)</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Plant Protein - Rich Chocolate (500 g / 1 kg / sachet)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Pepzyme Pro: protease + B. coagulans, B. subtilis, B. clausii</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Not declared</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Not declared</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Yes (premix)</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Pepzyme Pro</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Pack label image (OCR)</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>https://chicnutrix.com/products/plant-protein-rich-chocolate-1kg</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0876/3490/3327/files/6_b9e239c5-819b-4be6-970e-e27a1c2e2a2f.png</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>Marketed by Aeronutrix Sports Products; manufactured by Fullife Healthcare (Khalapur)</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>P41</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>AS-IT-IS</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>ATOM NXT Yeast Protein</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Bacillus coagulans (+ DigeZyme®)</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Not declared</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>1 bn CFU per serve</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Yes: B. coagulans</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Pack label image (OCR)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>https://asitisnutrition.com/products/as-it-is-atom-nxt-protein</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0005/5335/3267/files/ATOM_NXT_Protein_500g_Kesar_Kulfi_Product_Side_Gusset_Image_3bcb4e83-542d-4910-996b-e49d66e27533.jpg</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>Manufactured by Medizen Labs Pvt Ltd, Bengaluru</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>P42</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>AS-IT-IS</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>ATOM Whey Protein / Whey Protein XL</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>L. rhamnosus, B. bifidum, L. acidophilus, B. longum</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Not declared</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>1 bn CFU per serve</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>No (LAB): switch angle</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Pack label image (OCR)</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>https://asitisnutrition.com/products/atom-whey-protein</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0005/5335/3267/files/ATOM_Whey_Protein_With_Yeast_1kg_Double_Rich_Chocolate_Side_Gusset_1.jpg</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>Medizen Labs Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>P43</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Healthy Gut Probiotic Gummies (30s/60s)</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Gummy</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Bacillus subtilis</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>HS43</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>1.5 bn CFU per gummy; 3 bn per 2-gummy serve</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Yes: B. subtilis</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Named strain HS43 (supplier not verified)</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Pack label image (OCR) + official page</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>https://himalayawellness.in/products/healthy-gut-probiotic-gummies</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-60s-SIDE3-INDIA-13750-F39-FV.jpg</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>Manufactured by Sarvotham Care Ltd, Medak, Telangana</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>P44</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Florasante capsules</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Capsule</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>B. coagulans; B. subtilis; S. thermophilus</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>B. subtilis TO-A; S. thermophilus St-21; B. coagulans not named</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>B. coagulans 100 million; B. subtilis 10 million; St-21 1 bn CFU</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Yes: B. coagulans + B. subtilis</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Named strain TO-A (supplier not verified)</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Pack label image (OCR)</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>https://himalayawellness.in/products/florasante</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/FLORASANTECAPSULES10sBOTTLESIDE1INDIA15027RGBIMSJHI2600217.jpg</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>Manufactured by Allianz Biosciences Pvt Ltd, Puducherry</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>P45</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Max Protein (Zydus Wellness)</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Plant Protein (Swiss Chocolate, Creamy Vanilla, Alphonso Mango)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Pepzyme Pro: protease + B. coagulans, B. subtilis, B. clausii</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Not declared</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Not declared</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Yes (premix)</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Pepzyme Pro</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Pack ingredient image (OCR) + official page</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maxprotein.in/products/max-protein-plant-protein-swiss-chocolate</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0512/8827/7146/files/ingradients_8199a49a-8c11-47db-bf73-855260d96aa5.jpg</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>Brand owner/marketer Zydus Wellness Ltd; Yummy Food Specialities Pvt listed (FSSAI 10018047001013)</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>P46</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Complan (Zydus Wellness)</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Complan VieMax (Vanilla / Chocolate)</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Bacillus coagulans</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Unique IS-2</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Not shown</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Yes: B. coagulans</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>YES: Unique IS-2</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy listing (Apollo Pharmacy)</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.apollopharmacy.in/otc/complan-viemax-vanilla-flavour-400g-jar</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>Manufacturer/marketer: Zydus Wellness Ltd, Ahmedabad</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>P47</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Gritzo (Bright Lifecare)</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>SuperMilk Weight+ (13+ yrs) and other SuperMilk variants</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Bacillus coagulans</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Not declared</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>1 bn CFU (search snippet)</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Yes: B. coagulans</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Official product page</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>A (organism) / C (CFU)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gritzo.com/products/supermilk-weight-plus</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>Marketed by Bright Lifecare Pvt Ltd; manufactured by Sapiens Labs, Solan (HP); some variants reportedly by Maxcure Nutravedics (Haridwar), unverified</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>P48</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Little Joys (Mosaic Wellness)</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Nutrimix 7+ / MamaMix nutrition powders</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Powder</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>L. acidophilus, B. infantis, B. bifidum, B. coagulans, L. rhamnosus (+ DigeZyme®)</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Not declared</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Not declared per organism</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Yes: B. coagulans</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Official product page</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>https://ourlittlejoys.com/product/mamamix-nutrimix-7</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>Manufactured by Sapiens Labs (Baddi, HP); marketed by Mosaic Wellness Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>P49</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Nutrazee</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Pre Probiotic Gummies</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Gummy</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Bacillus coagulans</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Unique IS-2</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>2 bn CFU per gummy</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Yes: B. coagulans</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>YES: Unique IS-2</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Pack label image (OCR)</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>https://nutrazee.com/products/probiotic-prebiotic-gummies-supplement</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0072/8796/3757/files/8_a24f680a-a143-4974-b602-f93834a46894.jpg</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>Manufactured by Unique Biotech Ltd</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7063,7 +8388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8177,8 +9502,410 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Chicnutrix</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Aeronutrix Sports Products Pvt Ltd (Fullife group)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Fullife Healthcare Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Khalapur, Raigad, MH</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Verified (label)</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Fullife R&amp;D</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Fullife procurement (inferred)</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Premix (Pepzyme Pro)</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0876/3490/3327/files/J.jpg</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>AS-IT-IS</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Medizen Labs Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Site terms + labels</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Medizen Labs Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Avalahalli, Mysore Road, Bengaluru 560026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Verified (labels)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Medizen Labs</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Medizen Labs (inferred)</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Inferred: direct purchase</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0005/5335/3267/files/ATOM_NXT_Protein_500g_Kesar_Kulfi_Product_Side_Gusset_Image_3bcb4e83-542d-4910-996b-e49d66e27533.jpg
+https://asitisnutrition.com/policies/terms-of-service</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness Company, Makali, Bengaluru</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Labels</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Gummies: Sarvotham Care Ltd. Florasante: Allianz Biosciences Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Medak, Telangana; Puducherry</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Verified (labels)</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya R&amp;D</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-30s-SIDE2-INDIA-13750-F39-FV.jpg
+https://cdn.shopify.com/s/files/1/0272/4714/9155/files/FLORASANTECAPSULES10sCARTONSIDE1INDIA15027RGBIMSJHI2600217.jpg</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Max Protein / Complan</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Zydus Wellness Ltd</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Official page / pharmacy listing</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Max Protein: Yummy Food Specialities Pvt. Complan VieMax: not seen</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Verified (Max Protein page)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Zydus Wellness R&amp;D</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maxprotein.in/products/max-protein-plant-protein-swiss-chocolate
+https://www.apollopharmacy.in/otc/complan-viemax-vanilla-flavour-400g-jar</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Gritzo</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Bright Lifecare Pvt Ltd, Gurugram</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Official page</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Sapiens Labs</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Village Dhana Bagbania, Nalagarh/Baddi, Solan, HP</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Verified (official page)</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Bright Lifecare R&amp;D</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gritzo.com/products/supermilk-weight-plus</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Little Joys</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Mosaic Wellness Pvt Ltd, Thane</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Official page</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Sapiens Labs</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Baddi, Solan, HP</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Verified (official page)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Mosaic Wellness</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>https://ourlittlejoys.com/product/mamamix-nutrimix-7</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Nutrazee</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Nutrazee</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Unique Biotech Ltd</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Shameerpet, Telangana</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Verified (label)</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Unique Biotech (inferred)</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Competitor-locked</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0072/8796/3757/files/7_58a6f5ac-c333-43c8-947e-b877cafccfcb.jpg</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K19"/>
+  <autoFilter ref="A1:K26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8189,7 +9916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8885,8 +10612,270 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Sapiens Labs</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Village Dhana Bagbania, PO Manpura, Baddi/Nalagarh, Solan, HP</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Gritzo SuperMilk (B. coagulans); Little Joys Nutrimix/MamaMix (B. coagulans in a blend). Biozyme manufacturer reported at the same village (unverified)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Official brand pages (A/B)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Strong hub CMO for HealthKart and Mosaic Wellness kids' nutrition</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>D.K. Malhotra (founder; directory listing, unverified)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Website (sapienslabs.info); IndiaMART listing</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Apollo lookup: purchase/R&amp;D; send PRODURA spec pack</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gritzo.com/products/supermilk-weight-plus
+https://ourlittlejoys.com/product/mamamix-nutrimix-7
+https://www.indiamart.com/sapienslabs/about-us.html</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Medizen Labs Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Avalahalli, Mysore Road, Bengaluru</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Own brand AS-IT-IS: ATOM NXT (B. coagulans 1 bn), ATOM Whey (LAB)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Labels (A)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Strong: brand owner and manufacturer in one</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Apollo lookup</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0005/5335/3267/files/ATOM_NXT_Protein_500g_Kesar_Kulfi_Product_Side_Gusset_Image_3bcb4e83-542d-4910-996b-e49d66e27533.jpg</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Sarvotham Care Ltd</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Jeedipally Village, Medak, Telangana</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Healthy Gut Gummies (B. subtilis HS43)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Label (A)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Medium: gummy CMO using a Bacillus strain</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Apollo lookup</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-30s-SIDE2-INDIA-13750-F39-FV.jpg</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Allianz Biosciences Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Thiruvandar Koil, Puducherry</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Florasante (B. coagulans + B. subtilis TO-A)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Label (A)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>Apollo lookup</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/FLORASANTECAPSULES10sCARTONSIDE1INDIA15027RGBIMSJHI2600217.jpg</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Yummy Food Specialities Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Max Protein Plant Protein (Pepzyme Pro) for Zydus Wellness</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Official page (A)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Medium: protein CMO using a Bacillus premix</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Verify the address; Apollo lookup</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maxprotein.in/products/max-protein-plant-protein-swiss-chocolate</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J13"/>
+  <autoFilter ref="A1:J18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8897,7 +10886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -11364,8 +13353,76 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>C35</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Sapiens Labs</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>(CMO for Gritzo, Little Joys)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>D.K. Malhotra</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Founder (per directory listing)</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Executive / CMO owner</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.indiamart.com/sapienslabs/about-us.html</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Directory / search snippet</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>C (unverified)</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Website enquiry (sapienslabs.info)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Suitable for Apollo lookup</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N35"/>
+  <autoFilter ref="A1:N36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11376,7 +13433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11807,8 +13864,216 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Zydus Wellness</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Complan VieMax</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>B. coagulans Unique IS-2®</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Unique Biotech</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy listing (B)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Not seen</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Large FMCG using a competitor strain</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Alternate-strain approval / new SKU</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.apollopharmacy.in/otc/complan-viemax-vanilla-flavour-400g-jar</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Zydus Wellness</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Max Protein Plant Protein</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Pepzyme Pro™</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Specialty Enzymes &amp; Probiotics</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Pack image (A)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Yummy Food Specialities</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Supplier premix</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Three-organism alternative</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0512/8827/7146/files/ingradients_8199a49a-8c11-47db-bf73-855260d96aa5.jpg</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Healthy Gut Probiotic Gummies; Florasante</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>B. subtilis HS43; B. subtilis TO-A</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Supplier not verified</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Pack labels (A)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Sarvotham Care; Allianz Biosciences</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Named B. subtilis strains in place</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Alternate strain / new SKU</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-60s-SIDE3-INDIA-13750-F39-FV.jpg</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Nutrazee</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Pre Probiotic Gummies</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>B. coagulans Unique IS-2®</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Unique Biotech (also the CMO)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Pack label (A)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Unique Biotech</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Competitor-locked</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>New SKU only</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0072/8796/3757/files/8_a24f680a-a143-4974-b602-f93834a46894.jpg</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J8"/>
+  <autoFilter ref="A1:J12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11819,7 +14084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12126,8 +14391,143 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>AS-IT-IS / Medizen Labs</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>ATOM NXT label: B. coagulans 1 bn CFU; site terms name Medizen Labs as IP owner; labels name Medizen Labs as manufacturer</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Medizen buys directly</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Current supplier; decision-makers</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Gummies: B. subtilis HS43 1.5 bn/gummy, made by Sarvotham Care. Florasante: B. coagulans 100 mn + B. subtilis TO-A, made by Allianz Biosciences</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya specifies the strains</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Strain suppliers; vendor approval owner</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Zydus Wellness</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Max Protein plant protein lists Pepzyme Pro (official page/pack); Complan VieMax lists Unique IS-2 (pharmacy listing)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Central R&amp;D/procurement</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Decision-makers; Complan manufacturer</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Bright Lifecare (Gritzo)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Gritzo official page: B. coagulans, manufactured by Sapiens Labs</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Brand nominates strain</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CFU on pack (snippet says 1 bn)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Little Joys / Mosaic Wellness</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Official page: B. coagulans in the Nutrimix 7+ digestion blend; made by Sapiens Labs</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>CMO buys on brand spec</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12138,7 +14538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12418,8 +14818,116 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Zingavita</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Multivitamin probiotics are LAB only (made by Tactus Nutrasciences)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Label OCR</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>https://zingavita.com/products/multivitamins-with-prebiotics-probiotics</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Setu</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Probiotic and protein lines are LAB only (made by Nutralike Formulation)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Label OCR</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>https://setu.in/products/tummy-probiotic_new</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Epigamia</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Yogurt starter cultures only (S. thermophilus, L. bulgaricus)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Catalogue text</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.epigamia.com/</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>The Wellness Shop gut gummies</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>A search snippet claimed B. coagulans + B. subtilis 1 bn each, but the product page now returns 404</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Not verifiable</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.thewellnessshop.in/products/gut-health-gummies</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:E14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12430,7 +14938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -14419,8 +16927,536 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>https://asitisnutrition.com/policies/terms-of-service</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Medizen Labs owns AS-IT-IS site</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Official page</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>https://www.indiamart.com/sapienslabs/about-us.html</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Sapiens Labs profile</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Directory (secondary)</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>https://ourlittlejoys.com/product/nutrimix-lite-1kg</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Little Joys Nutrimix Lite 5 bn CFU</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Official page</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>https://chicnutrix.com/products/plant-protein-rich-chocolate-1kg</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Chicnutrix (Fullife): Plant Protein - Rich Chocolate (500 g / 1 kg / sachet) (product page)</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0876/3490/3327/files/6_b9e239c5-819b-4be6-970e-e27a1c2e2a2f.png</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Chicnutrix (Fullife): pack/label image</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image (brand CDN)</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>https://asitisnutrition.com/products/as-it-is-atom-nxt-protein</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>AS-IT-IS: ATOM NXT Yeast Protein (product page)</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0005/5335/3267/files/ATOM_NXT_Protein_500g_Kesar_Kulfi_Product_Side_Gusset_Image_3bcb4e83-542d-4910-996b-e49d66e27533.jpg</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>AS-IT-IS: pack/label image</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image (brand CDN)</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>https://asitisnutrition.com/products/atom-whey-protein</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>AS-IT-IS: ATOM Whey Protein / Whey Protein XL (product page)</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0005/5335/3267/files/ATOM_Whey_Protein_With_Yeast_1kg_Double_Rich_Chocolate_Side_Gusset_1.jpg</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>AS-IT-IS: pack/label image</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image (brand CDN)</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>https://himalayawellness.in/products/healthy-gut-probiotic-gummies</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness: Healthy Gut Probiotic Gummies (30s/60s) (product page)</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-60s-SIDE3-INDIA-13750-F39-FV.jpg</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness: pack/label image</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image (brand CDN)</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>https://himalayawellness.in/products/florasante</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness: Florasante capsules (product page)</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/FLORASANTECAPSULES10sBOTTLESIDE1INDIA15027RGBIMSJHI2600217.jpg</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya Wellness: pack/label image</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image (brand CDN)</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>https://www.maxprotein.in/products/max-protein-plant-protein-swiss-chocolate</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Max Protein (Zydus Wellness): Plant Protein (Swiss Chocolate, Creamy Vanilla, Alphonso Mango) (product page)</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0512/8827/7146/files/ingradients_8199a49a-8c11-47db-bf73-855260d96aa5.jpg</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Max Protein (Zydus Wellness): pack/label image</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image (brand CDN)</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>https://www.apollopharmacy.in/otc/complan-viemax-vanilla-flavour-400g-jar</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Complan (Zydus Wellness): Complan VieMax (Vanilla / Chocolate) (product page)</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gritzo.com/products/supermilk-weight-plus</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Gritzo (Bright Lifecare): SuperMilk Weight+ (13+ yrs) and other SuperMilk variants (product page)</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>https://ourlittlejoys.com/product/mamamix-nutrimix-7</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Little Joys (Mosaic Wellness): Nutrimix 7+ / MamaMix nutrition powders (product page)</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>https://nutrazee.com/products/probiotic-prebiotic-gummies-supplement</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Nutrazee: Pre Probiotic Gummies (product page)</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Official product page / listing</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0072/8796/3757/files/8_a24f680a-a143-4974-b602-f93834a46894.jpg</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Nutrazee: pack/label image</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image (brand CDN)</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0876/3490/3327/files/J.jpg</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Chicnutrix manufacturer label</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/HEALTHY-GUT-GUMMIES-30s-SIDE2-INDIA-13750-F39-FV.jpg</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Himalaya gummies manufacturer label</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0272/4714/9155/files/FLORASANTECAPSULES10sCARTONSIDE1INDIA15027RGBIMSJHI2600217.jpg</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Florasante manufacturer label</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0072/8796/3757/files/7_58a6f5ac-c333-43c8-947e-b877cafccfcb.jpg</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Nutrazee manufacturer label</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Official pack image</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D90"/>
+  <autoFilter ref="A1:D114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>